--- a/uts/outputHDBSCAN/evaluasi_hdbscan_cosine.xlsx
+++ b/uts/outputHDBSCAN/evaluasi_hdbscan_cosine.xlsx
@@ -541,7 +541,7 @@
         <v>1890.15</v>
       </c>
       <c r="M2" t="n">
-        <v>118.49736</v>
+        <v>62.12746</v>
       </c>
       <c r="N2" t="n">
         <v>10000</v>
